--- a/outputs/Exchange_rate_percentile_classification_matrix.xlsx
+++ b/outputs/Exchange_rate_percentile_classification_matrix.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2625" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2625" uniqueCount="125">
   <si>
     <t>2020 May</t>
   </si>
@@ -344,6 +344,9 @@
   </si>
   <si>
     <t>Minimal</t>
+  </si>
+  <si>
+    <t>No data</t>
   </si>
   <si>
     <t>Alarm</t>
@@ -1051,31 +1054,31 @@
         <v>109</v>
       </c>
       <c r="S2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="T2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="U2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="V2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="W2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="X2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="Y2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="Z2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AA2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AB2" t="s">
         <v>109</v>
@@ -1084,31 +1087,31 @@
         <v>109</v>
       </c>
       <c r="AD2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="AE2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AF2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AG2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AH2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AI2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AJ2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AK2" t="s">
         <v>109</v>
       </c>
       <c r="AL2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AM2" t="s">
         <v>109</v>
@@ -1213,13 +1216,13 @@
         <v>109</v>
       </c>
       <c r="BU2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="BV2" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="BW2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="3" spans="1:75">
@@ -1278,34 +1281,34 @@
         <v>109</v>
       </c>
       <c r="S3" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="T3" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="U3" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="V3" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="W3" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="X3" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="Y3" t="s">
         <v>109</v>
       </c>
       <c r="Z3" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AA3" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AB3" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AC3" t="s">
         <v>109</v>
@@ -1314,22 +1317,22 @@
         <v>109</v>
       </c>
       <c r="AE3" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AF3" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AG3" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AH3" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AI3" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AJ3" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AK3" t="s">
         <v>109</v>
@@ -1440,13 +1443,13 @@
         <v>109</v>
       </c>
       <c r="BU3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="BV3" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="BW3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="4" spans="1:75">
@@ -1505,34 +1508,34 @@
         <v>109</v>
       </c>
       <c r="S4" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="T4" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="U4" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="V4" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="W4" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="X4" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="Y4" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="Z4" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AA4" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AB4" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AC4" t="s">
         <v>109</v>
@@ -1541,28 +1544,28 @@
         <v>109</v>
       </c>
       <c r="AE4" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AF4" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AG4" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AH4" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AI4" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AJ4" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AK4" t="s">
         <v>109</v>
       </c>
       <c r="AL4" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AM4" t="s">
         <v>109</v>
@@ -1667,13 +1670,13 @@
         <v>109</v>
       </c>
       <c r="BU4" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="BV4" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="BW4" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="5" spans="1:75">
@@ -1732,34 +1735,34 @@
         <v>109</v>
       </c>
       <c r="S5" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="T5" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="U5" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="V5" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="W5" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="X5" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="Y5" t="s">
         <v>109</v>
       </c>
       <c r="Z5" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AA5" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AB5" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="AC5" t="s">
         <v>109</v>
@@ -1768,28 +1771,28 @@
         <v>109</v>
       </c>
       <c r="AE5" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AF5" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AG5" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AH5" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AI5" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AJ5" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AK5" t="s">
         <v>109</v>
       </c>
       <c r="AL5" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="AM5" t="s">
         <v>109</v>
@@ -1894,13 +1897,13 @@
         <v>109</v>
       </c>
       <c r="BU5" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="BV5" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="BW5" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="6" spans="1:75">
@@ -1959,34 +1962,34 @@
         <v>109</v>
       </c>
       <c r="S6" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="T6" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="U6" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="V6" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="W6" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="X6" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="Y6" t="s">
         <v>109</v>
       </c>
       <c r="Z6" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AA6" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AB6" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="AC6" t="s">
         <v>109</v>
@@ -1995,28 +1998,28 @@
         <v>109</v>
       </c>
       <c r="AE6" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AF6" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AG6" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AH6" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AI6" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AJ6" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AK6" t="s">
         <v>109</v>
       </c>
       <c r="AL6" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AM6" t="s">
         <v>109</v>
@@ -2121,13 +2124,13 @@
         <v>109</v>
       </c>
       <c r="BU6" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="BV6" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="BW6" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="7" spans="1:75">
@@ -2186,34 +2189,34 @@
         <v>109</v>
       </c>
       <c r="S7" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="T7" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="U7" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="V7" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="W7" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="X7" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="Y7" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="Z7" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AA7" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AB7" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="AC7" t="s">
         <v>109</v>
@@ -2222,28 +2225,28 @@
         <v>109</v>
       </c>
       <c r="AE7" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AF7" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AG7" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AH7" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AI7" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AJ7" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AK7" t="s">
         <v>109</v>
       </c>
       <c r="AL7" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AM7" t="s">
         <v>109</v>
@@ -2348,13 +2351,13 @@
         <v>109</v>
       </c>
       <c r="BU7" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="BV7" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="BW7" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="8" spans="1:75">
@@ -2413,31 +2416,31 @@
         <v>109</v>
       </c>
       <c r="S8" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="T8" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="U8" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="V8" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="W8" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="X8" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="Y8" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="Z8" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AA8" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AB8" t="s">
         <v>109</v>
@@ -2449,28 +2452,28 @@
         <v>109</v>
       </c>
       <c r="AE8" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AF8" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AG8" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AH8" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AI8" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AJ8" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AK8" t="s">
         <v>109</v>
       </c>
       <c r="AL8" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AM8" t="s">
         <v>109</v>
@@ -2575,13 +2578,13 @@
         <v>109</v>
       </c>
       <c r="BU8" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="BV8" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="BW8" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="9" spans="1:75">
@@ -2640,64 +2643,64 @@
         <v>109</v>
       </c>
       <c r="S9" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="T9" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="U9" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="V9" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="W9" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="X9" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="Y9" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="Z9" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AA9" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AB9" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="AC9" t="s">
         <v>109</v>
       </c>
       <c r="AD9" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="AE9" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AF9" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AG9" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AH9" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AI9" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AJ9" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AK9" t="s">
         <v>109</v>
       </c>
       <c r="AL9" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AM9" t="s">
         <v>109</v>
@@ -2802,13 +2805,13 @@
         <v>109</v>
       </c>
       <c r="BU9" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="BV9" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="BW9" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="10" spans="1:75">
@@ -2867,34 +2870,34 @@
         <v>109</v>
       </c>
       <c r="S10" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="T10" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="U10" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="V10" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="W10" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="X10" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="Y10" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="Z10" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AA10" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AB10" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AC10" t="s">
         <v>109</v>
@@ -2903,28 +2906,28 @@
         <v>109</v>
       </c>
       <c r="AE10" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AF10" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AG10" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AH10" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AI10" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AJ10" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AK10" t="s">
         <v>109</v>
       </c>
       <c r="AL10" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AM10" t="s">
         <v>109</v>
@@ -3029,13 +3032,13 @@
         <v>109</v>
       </c>
       <c r="BU10" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="BV10" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="BW10" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="11" spans="1:75">
@@ -3094,22 +3097,22 @@
         <v>109</v>
       </c>
       <c r="S11" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="T11" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="U11" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="V11" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="W11" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="X11" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="Y11" t="s">
         <v>109</v>
@@ -3118,7 +3121,7 @@
         <v>109</v>
       </c>
       <c r="AA11" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="AB11" t="s">
         <v>109</v>
@@ -3130,22 +3133,22 @@
         <v>109</v>
       </c>
       <c r="AE11" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="AF11" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AG11" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AH11" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AI11" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AJ11" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AK11" t="s">
         <v>109</v>
@@ -3256,13 +3259,13 @@
         <v>109</v>
       </c>
       <c r="BU11" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="BV11" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="BW11" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="12" spans="1:75">
@@ -3321,64 +3324,64 @@
         <v>109</v>
       </c>
       <c r="S12" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="T12" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="U12" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="V12" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="W12" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="X12" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="Y12" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="Z12" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AA12" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AB12" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AC12" t="s">
         <v>109</v>
       </c>
       <c r="AD12" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AE12" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AF12" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AG12" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AH12" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AI12" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AJ12" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AK12" t="s">
         <v>109</v>
       </c>
       <c r="AL12" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AM12" t="s">
         <v>109</v>
@@ -3483,13 +3486,13 @@
         <v>109</v>
       </c>
       <c r="BU12" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="BV12" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="BW12" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="13" spans="1:75">
@@ -3548,58 +3551,58 @@
         <v>109</v>
       </c>
       <c r="S13" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="T13" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="U13" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="V13" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="W13" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="X13" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="Y13" t="s">
         <v>109</v>
       </c>
       <c r="Z13" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AA13" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AB13" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="AC13" t="s">
         <v>109</v>
       </c>
       <c r="AD13" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="AE13" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AF13" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AG13" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AH13" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AI13" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AJ13" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AK13" t="s">
         <v>109</v>
@@ -3710,13 +3713,13 @@
         <v>109</v>
       </c>
       <c r="BU13" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="BV13" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="BW13" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="14" spans="1:75">
@@ -3775,31 +3778,31 @@
         <v>109</v>
       </c>
       <c r="S14" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="T14" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="U14" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="V14" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="W14" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="X14" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="Y14" t="s">
         <v>109</v>
       </c>
       <c r="Z14" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AA14" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AB14" t="s">
         <v>109</v>
@@ -3808,31 +3811,31 @@
         <v>109</v>
       </c>
       <c r="AD14" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AE14" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AF14" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AG14" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AH14" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AI14" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AJ14" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AK14" t="s">
         <v>109</v>
       </c>
       <c r="AL14" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AM14" t="s">
         <v>109</v>
@@ -3937,13 +3940,13 @@
         <v>109</v>
       </c>
       <c r="BU14" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="BV14" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="BW14" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="15" spans="1:75">
@@ -3951,154 +3954,154 @@
         <v>88</v>
       </c>
       <c r="B15" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C15" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D15" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E15" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F15" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="G15" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="H15" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="I15" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="J15" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="K15" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="L15" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="M15" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="N15" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="O15" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="P15" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="Q15" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="R15" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="S15" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="T15" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="U15" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="V15" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="W15" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="X15" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="Y15" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="Z15" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AA15" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AB15" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AC15" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AD15" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AE15" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AF15" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AG15" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AH15" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AI15" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AJ15" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AK15" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AL15" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AM15" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AN15" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AO15" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AP15" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AQ15" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AR15" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AS15" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AT15" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AU15" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AV15" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AW15" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AX15" t="s">
         <v>109</v>
       </c>
       <c r="AY15" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AZ15" t="s">
         <v>109</v>
@@ -4119,7 +4122,7 @@
         <v>109</v>
       </c>
       <c r="BF15" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="BG15" t="s">
         <v>109</v>
@@ -4128,28 +4131,28 @@
         <v>109</v>
       </c>
       <c r="BI15" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="BJ15" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="BK15" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="BL15" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="BM15" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="BN15" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="BO15" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="BP15" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="BQ15" t="s">
         <v>109</v>
@@ -4158,19 +4161,19 @@
         <v>109</v>
       </c>
       <c r="BS15" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="BT15" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="BU15" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="BV15" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="BW15" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="16" spans="1:75">
@@ -4229,58 +4232,58 @@
         <v>109</v>
       </c>
       <c r="S16" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="T16" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="U16" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="V16" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="W16" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="X16" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="Y16" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="Z16" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AA16" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AB16" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AC16" t="s">
         <v>109</v>
       </c>
       <c r="AD16" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="AE16" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AF16" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AG16" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AH16" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AI16" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AJ16" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AK16" t="s">
         <v>109</v>
@@ -4391,13 +4394,13 @@
         <v>109</v>
       </c>
       <c r="BU16" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="BV16" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="BW16" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="17" spans="1:75">
@@ -4456,64 +4459,64 @@
         <v>109</v>
       </c>
       <c r="S17" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="T17" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="U17" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="V17" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="W17" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="X17" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="Y17" t="s">
         <v>109</v>
       </c>
       <c r="Z17" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AA17" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AB17" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="AC17" t="s">
         <v>109</v>
       </c>
       <c r="AD17" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AE17" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AF17" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AG17" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AH17" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AI17" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AJ17" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AK17" t="s">
         <v>109</v>
       </c>
       <c r="AL17" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="AM17" t="s">
         <v>109</v>
@@ -4618,13 +4621,13 @@
         <v>109</v>
       </c>
       <c r="BU17" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="BV17" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="BW17" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="18" spans="1:75">
@@ -4683,34 +4686,34 @@
         <v>109</v>
       </c>
       <c r="S18" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="T18" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="U18" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="V18" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="W18" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="X18" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="Y18" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="Z18" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AA18" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AB18" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="AC18" t="s">
         <v>109</v>
@@ -4719,28 +4722,28 @@
         <v>109</v>
       </c>
       <c r="AE18" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AF18" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AG18" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AH18" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AI18" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AJ18" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AK18" t="s">
         <v>109</v>
       </c>
       <c r="AL18" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="AM18" t="s">
         <v>109</v>
@@ -4845,13 +4848,13 @@
         <v>109</v>
       </c>
       <c r="BU18" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="BV18" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="BW18" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="19" spans="1:75">
@@ -4910,31 +4913,31 @@
         <v>109</v>
       </c>
       <c r="S19" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="T19" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="U19" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="V19" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="W19" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="X19" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="Y19" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="Z19" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AA19" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AB19" t="s">
         <v>109</v>
@@ -4946,28 +4949,28 @@
         <v>109</v>
       </c>
       <c r="AE19" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AF19" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AG19" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AH19" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AI19" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AJ19" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AK19" t="s">
         <v>109</v>
       </c>
       <c r="AL19" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AM19" t="s">
         <v>109</v>
@@ -5072,13 +5075,13 @@
         <v>109</v>
       </c>
       <c r="BU19" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="BV19" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="BW19" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="20" spans="1:75">
@@ -5137,31 +5140,31 @@
         <v>109</v>
       </c>
       <c r="S20" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="T20" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="U20" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="V20" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="W20" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="X20" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="Y20" t="s">
         <v>109</v>
       </c>
       <c r="Z20" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AA20" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AB20" t="s">
         <v>109</v>
@@ -5173,28 +5176,28 @@
         <v>109</v>
       </c>
       <c r="AE20" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AF20" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AG20" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AH20" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AI20" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AJ20" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AK20" t="s">
         <v>109</v>
       </c>
       <c r="AL20" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AM20" t="s">
         <v>109</v>
@@ -5299,13 +5302,13 @@
         <v>109</v>
       </c>
       <c r="BU20" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="BV20" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="BW20" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="21" spans="1:75">
@@ -5364,34 +5367,34 @@
         <v>109</v>
       </c>
       <c r="S21" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="T21" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="U21" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="V21" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="W21" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="X21" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="Y21" t="s">
         <v>109</v>
       </c>
       <c r="Z21" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AA21" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AB21" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="AC21" t="s">
         <v>109</v>
@@ -5400,28 +5403,28 @@
         <v>109</v>
       </c>
       <c r="AE21" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AF21" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AG21" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AH21" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AI21" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AJ21" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AK21" t="s">
         <v>109</v>
       </c>
       <c r="AL21" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AM21" t="s">
         <v>109</v>
@@ -5526,13 +5529,13 @@
         <v>109</v>
       </c>
       <c r="BU21" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="BV21" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="BW21" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="22" spans="1:75">
@@ -5591,34 +5594,34 @@
         <v>109</v>
       </c>
       <c r="S22" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="T22" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="U22" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="V22" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="W22" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="X22" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="Y22" t="s">
         <v>109</v>
       </c>
       <c r="Z22" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AA22" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AB22" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="AC22" t="s">
         <v>109</v>
@@ -5627,28 +5630,28 @@
         <v>109</v>
       </c>
       <c r="AE22" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AF22" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AG22" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AH22" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AI22" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AJ22" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AK22" t="s">
         <v>109</v>
       </c>
       <c r="AL22" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AM22" t="s">
         <v>109</v>
@@ -5753,13 +5756,13 @@
         <v>109</v>
       </c>
       <c r="BU22" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="BV22" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="BW22" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="23" spans="1:75">
@@ -5818,31 +5821,31 @@
         <v>109</v>
       </c>
       <c r="S23" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="T23" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="U23" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="V23" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="W23" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="X23" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="Y23" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="Z23" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AA23" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AB23" t="s">
         <v>109</v>
@@ -5851,31 +5854,31 @@
         <v>109</v>
       </c>
       <c r="AD23" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="AE23" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AF23" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AG23" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AH23" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AI23" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AJ23" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AK23" t="s">
         <v>109</v>
       </c>
       <c r="AL23" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AM23" t="s">
         <v>109</v>
@@ -5980,13 +5983,13 @@
         <v>109</v>
       </c>
       <c r="BU23" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="BV23" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="BW23" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="24" spans="1:75">
@@ -6045,34 +6048,34 @@
         <v>109</v>
       </c>
       <c r="S24" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="T24" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="U24" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="V24" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="W24" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="X24" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="Y24" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="Z24" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AA24" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AB24" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AC24" t="s">
         <v>109</v>
@@ -6081,28 +6084,28 @@
         <v>109</v>
       </c>
       <c r="AE24" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AF24" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AG24" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AH24" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AI24" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AJ24" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AK24" t="s">
         <v>109</v>
       </c>
       <c r="AL24" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AM24" t="s">
         <v>109</v>
@@ -6207,13 +6210,13 @@
         <v>109</v>
       </c>
       <c r="BU24" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="BV24" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="BW24" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="25" spans="1:75">
@@ -6272,31 +6275,31 @@
         <v>109</v>
       </c>
       <c r="S25" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="T25" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="U25" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="V25" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="W25" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="X25" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="Y25" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="Z25" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AA25" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AB25" t="s">
         <v>109</v>
@@ -6308,28 +6311,28 @@
         <v>109</v>
       </c>
       <c r="AE25" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AF25" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AG25" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AH25" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AI25" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AJ25" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AK25" t="s">
         <v>109</v>
       </c>
       <c r="AL25" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="AM25" t="s">
         <v>109</v>
@@ -6434,13 +6437,13 @@
         <v>109</v>
       </c>
       <c r="BU25" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="BV25" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="BW25" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="26" spans="1:75">
@@ -6499,31 +6502,31 @@
         <v>109</v>
       </c>
       <c r="S26" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="T26" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="U26" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="V26" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="W26" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="X26" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="Y26" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="Z26" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AA26" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AB26" t="s">
         <v>109</v>
@@ -6532,31 +6535,31 @@
         <v>109</v>
       </c>
       <c r="AD26" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="AE26" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AF26" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AG26" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AH26" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AI26" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AJ26" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AK26" t="s">
         <v>109</v>
       </c>
       <c r="AL26" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AM26" t="s">
         <v>109</v>
@@ -6661,13 +6664,13 @@
         <v>109</v>
       </c>
       <c r="BU26" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="BV26" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="BW26" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="27" spans="1:75">
@@ -6732,10 +6735,10 @@
         <v>109</v>
       </c>
       <c r="U27" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="V27" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="W27" t="s">
         <v>109</v>
@@ -6747,154 +6750,154 @@
         <v>109</v>
       </c>
       <c r="Z27" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AA27" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AB27" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AC27" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AD27" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AE27" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AF27" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AG27" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AH27" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AI27" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AJ27" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AK27" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AL27" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AM27" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AN27" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AO27" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AP27" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AQ27" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AR27" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AS27" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AT27" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AU27" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AV27" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AW27" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AX27" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AY27" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AZ27" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="BA27" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="BB27" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="BC27" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="BD27" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="BE27" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="BF27" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="BG27" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="BH27" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="BI27" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="BJ27" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="BK27" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="BL27" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="BM27" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="BN27" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="BO27" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="BP27" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="BQ27" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="BR27" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="BS27" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="BT27" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="BU27" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="BV27" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="BW27" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="28" spans="1:75">
@@ -6953,64 +6956,64 @@
         <v>109</v>
       </c>
       <c r="S28" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="T28" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="U28" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="V28" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="W28" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="X28" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="Y28" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="Z28" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AA28" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AB28" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AC28" t="s">
         <v>109</v>
       </c>
       <c r="AD28" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AE28" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AF28" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AG28" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AH28" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AI28" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AJ28" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AK28" t="s">
         <v>109</v>
       </c>
       <c r="AL28" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AM28" t="s">
         <v>109</v>
@@ -7115,13 +7118,13 @@
         <v>109</v>
       </c>
       <c r="BU28" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="BV28" t="s">
+        <v>121</v>
+      </c>
+      <c r="BW28" t="s">
         <v>120</v>
-      </c>
-      <c r="BW28" t="s">
-        <v>119</v>
       </c>
     </row>
     <row r="29" spans="1:75">
@@ -7180,31 +7183,31 @@
         <v>109</v>
       </c>
       <c r="S29" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="T29" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="U29" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="V29" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="W29" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="X29" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="Y29" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="Z29" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AA29" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AB29" t="s">
         <v>109</v>
@@ -7213,31 +7216,31 @@
         <v>109</v>
       </c>
       <c r="AD29" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="AE29" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AF29" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AG29" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AH29" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AI29" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AJ29" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AK29" t="s">
         <v>109</v>
       </c>
       <c r="AL29" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AM29" t="s">
         <v>109</v>
@@ -7342,13 +7345,13 @@
         <v>109</v>
       </c>
       <c r="BU29" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="BV29" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="BW29" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="30" spans="1:75">
@@ -7404,34 +7407,34 @@
         <v>109</v>
       </c>
       <c r="R30" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="S30" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="T30" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="U30" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="V30" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="W30" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="X30" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="Y30" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="Z30" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AA30" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AB30" t="s">
         <v>109</v>
@@ -7440,31 +7443,31 @@
         <v>109</v>
       </c>
       <c r="AD30" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AE30" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AF30" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AG30" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AH30" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AI30" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AJ30" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AK30" t="s">
         <v>109</v>
       </c>
       <c r="AL30" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="AM30" t="s">
         <v>109</v>
@@ -7569,13 +7572,13 @@
         <v>109</v>
       </c>
       <c r="BU30" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="BV30" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="BW30" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="31" spans="1:75">
@@ -7634,31 +7637,31 @@
         <v>109</v>
       </c>
       <c r="S31" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="T31" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="U31" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="V31" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="W31" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="X31" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="Y31" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="Z31" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AA31" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AB31" t="s">
         <v>109</v>
@@ -7667,31 +7670,31 @@
         <v>109</v>
       </c>
       <c r="AD31" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AE31" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AF31" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AG31" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AH31" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AI31" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AJ31" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AK31" t="s">
         <v>109</v>
       </c>
       <c r="AL31" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AM31" t="s">
         <v>109</v>
@@ -7796,13 +7799,13 @@
         <v>109</v>
       </c>
       <c r="BU31" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="BV31" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="BW31" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="32" spans="1:75">
@@ -7861,64 +7864,64 @@
         <v>109</v>
       </c>
       <c r="S32" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="T32" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="U32" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="V32" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="W32" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="X32" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="Y32" t="s">
         <v>109</v>
       </c>
       <c r="Z32" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AA32" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AB32" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AC32" t="s">
         <v>109</v>
       </c>
       <c r="AD32" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AE32" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AF32" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AG32" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AH32" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AI32" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AJ32" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AK32" t="s">
         <v>109</v>
       </c>
       <c r="AL32" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AM32" t="s">
         <v>109</v>
@@ -8023,13 +8026,13 @@
         <v>109</v>
       </c>
       <c r="BU32" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="BV32" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="BW32" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="33" spans="1:75">
@@ -8088,64 +8091,64 @@
         <v>109</v>
       </c>
       <c r="S33" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="T33" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="U33" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="V33" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="W33" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="X33" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="Y33" t="s">
         <v>109</v>
       </c>
       <c r="Z33" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AA33" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AB33" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AC33" t="s">
         <v>109</v>
       </c>
       <c r="AD33" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AE33" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AF33" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AG33" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AH33" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AI33" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AJ33" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AK33" t="s">
         <v>109</v>
       </c>
       <c r="AL33" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AM33" t="s">
         <v>109</v>
@@ -8250,13 +8253,13 @@
         <v>109</v>
       </c>
       <c r="BU33" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="BV33" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="BW33" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="34" spans="1:75">
@@ -8315,31 +8318,31 @@
         <v>109</v>
       </c>
       <c r="S34" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="T34" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="U34" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="V34" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="W34" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="X34" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="Y34" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="Z34" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AA34" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AB34" t="s">
         <v>109</v>
@@ -8348,31 +8351,31 @@
         <v>109</v>
       </c>
       <c r="AD34" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="AE34" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="AF34" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AG34" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AH34" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AI34" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AJ34" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AK34" t="s">
         <v>109</v>
       </c>
       <c r="AL34" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AM34" t="s">
         <v>109</v>
@@ -8477,13 +8480,13 @@
         <v>109</v>
       </c>
       <c r="BU34" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="BV34" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="BW34" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="35" spans="1:75">
@@ -8542,31 +8545,31 @@
         <v>109</v>
       </c>
       <c r="S35" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="T35" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="U35" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="V35" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="W35" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="X35" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="Y35" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="Z35" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AA35" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AB35" t="s">
         <v>109</v>
@@ -8578,22 +8581,22 @@
         <v>109</v>
       </c>
       <c r="AE35" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AF35" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AG35" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AH35" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AI35" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AJ35" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AK35" t="s">
         <v>109</v>
@@ -8704,13 +8707,13 @@
         <v>109</v>
       </c>
       <c r="BU35" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="BV35" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="BW35" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/Exchange_rate_percentile_classification_matrix.xlsx
+++ b/outputs/Exchange_rate_percentile_classification_matrix.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2625" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2625" uniqueCount="112">
   <si>
     <t>2020 May</t>
   </si>
@@ -349,46 +349,7 @@
     <t>No data</t>
   </si>
   <si>
-    <t>Alarm</t>
-  </si>
-  <si>
-    <t>Alert</t>
-  </si>
-  <si>
-    <t>21%</t>
-  </si>
-  <si>
-    <t>24%</t>
-  </si>
-  <si>
-    <t>20%</t>
-  </si>
-  <si>
-    <t>23%</t>
-  </si>
-  <si>
-    <t>15%</t>
-  </si>
-  <si>
-    <t>6%</t>
-  </si>
-  <si>
-    <t>3%</t>
-  </si>
-  <si>
-    <t>25%</t>
-  </si>
-  <si>
     <t>0%</t>
-  </si>
-  <si>
-    <t>1%</t>
-  </si>
-  <si>
-    <t>4%</t>
-  </si>
-  <si>
-    <t>18%</t>
   </si>
 </sst>
 </file>
@@ -1054,31 +1015,31 @@
         <v>109</v>
       </c>
       <c r="S2" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="T2" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="U2" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="V2" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="W2" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="X2" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="Y2" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="Z2" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AA2" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AB2" t="s">
         <v>109</v>
@@ -1087,31 +1048,31 @@
         <v>109</v>
       </c>
       <c r="AD2" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="AE2" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AF2" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AG2" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AH2" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AI2" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AJ2" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AK2" t="s">
         <v>109</v>
       </c>
       <c r="AL2" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AM2" t="s">
         <v>109</v>
@@ -1216,13 +1177,13 @@
         <v>109</v>
       </c>
       <c r="BU2" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="BV2" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="BW2" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
     </row>
     <row r="3" spans="1:75">
@@ -1281,34 +1242,34 @@
         <v>109</v>
       </c>
       <c r="S3" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="T3" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="U3" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="V3" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="W3" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="X3" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="Y3" t="s">
         <v>109</v>
       </c>
       <c r="Z3" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AA3" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AB3" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AC3" t="s">
         <v>109</v>
@@ -1317,22 +1278,22 @@
         <v>109</v>
       </c>
       <c r="AE3" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AF3" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AG3" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AH3" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AI3" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AJ3" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AK3" t="s">
         <v>109</v>
@@ -1443,13 +1404,13 @@
         <v>109</v>
       </c>
       <c r="BU3" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="BV3" t="s">
-        <v>121</v>
+        <v>111</v>
       </c>
       <c r="BW3" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="4" spans="1:75">
@@ -1508,34 +1469,34 @@
         <v>109</v>
       </c>
       <c r="S4" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="T4" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="U4" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="V4" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="W4" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="X4" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="Y4" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="Z4" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AA4" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AB4" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AC4" t="s">
         <v>109</v>
@@ -1544,28 +1505,28 @@
         <v>109</v>
       </c>
       <c r="AE4" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AF4" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AG4" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AH4" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AI4" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AJ4" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AK4" t="s">
         <v>109</v>
       </c>
       <c r="AL4" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AM4" t="s">
         <v>109</v>
@@ -1670,13 +1631,13 @@
         <v>109</v>
       </c>
       <c r="BU4" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="BV4" t="s">
-        <v>121</v>
+        <v>111</v>
       </c>
       <c r="BW4" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
     </row>
     <row r="5" spans="1:75">
@@ -1735,34 +1696,34 @@
         <v>109</v>
       </c>
       <c r="S5" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="T5" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="U5" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="V5" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="W5" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="X5" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="Y5" t="s">
         <v>109</v>
       </c>
       <c r="Z5" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AA5" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AB5" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="AC5" t="s">
         <v>109</v>
@@ -1771,28 +1732,28 @@
         <v>109</v>
       </c>
       <c r="AE5" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AF5" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AG5" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AH5" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AI5" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AJ5" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AK5" t="s">
         <v>109</v>
       </c>
       <c r="AL5" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="AM5" t="s">
         <v>109</v>
@@ -1897,13 +1858,13 @@
         <v>109</v>
       </c>
       <c r="BU5" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="BV5" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="BW5" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
     </row>
     <row r="6" spans="1:75">
@@ -1962,34 +1923,34 @@
         <v>109</v>
       </c>
       <c r="S6" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="T6" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="U6" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="V6" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="W6" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="X6" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="Y6" t="s">
         <v>109</v>
       </c>
       <c r="Z6" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AA6" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AB6" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="AC6" t="s">
         <v>109</v>
@@ -1998,28 +1959,28 @@
         <v>109</v>
       </c>
       <c r="AE6" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AF6" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AG6" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AH6" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AI6" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AJ6" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AK6" t="s">
         <v>109</v>
       </c>
       <c r="AL6" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AM6" t="s">
         <v>109</v>
@@ -2124,13 +2085,13 @@
         <v>109</v>
       </c>
       <c r="BU6" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="BV6" t="s">
-        <v>122</v>
+        <v>111</v>
       </c>
       <c r="BW6" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
     </row>
     <row r="7" spans="1:75">
@@ -2189,34 +2150,34 @@
         <v>109</v>
       </c>
       <c r="S7" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="T7" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="U7" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="V7" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="W7" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="X7" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="Y7" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="Z7" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AA7" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AB7" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="AC7" t="s">
         <v>109</v>
@@ -2225,28 +2186,28 @@
         <v>109</v>
       </c>
       <c r="AE7" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AF7" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AG7" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AH7" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AI7" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AJ7" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AK7" t="s">
         <v>109</v>
       </c>
       <c r="AL7" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AM7" t="s">
         <v>109</v>
@@ -2351,13 +2312,13 @@
         <v>109</v>
       </c>
       <c r="BU7" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="BV7" t="s">
-        <v>122</v>
+        <v>111</v>
       </c>
       <c r="BW7" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
     </row>
     <row r="8" spans="1:75">
@@ -2416,31 +2377,31 @@
         <v>109</v>
       </c>
       <c r="S8" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="T8" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="U8" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="V8" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="W8" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="X8" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="Y8" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="Z8" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AA8" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AB8" t="s">
         <v>109</v>
@@ -2452,28 +2413,28 @@
         <v>109</v>
       </c>
       <c r="AE8" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AF8" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AG8" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AH8" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AI8" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AJ8" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AK8" t="s">
         <v>109</v>
       </c>
       <c r="AL8" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AM8" t="s">
         <v>109</v>
@@ -2578,13 +2539,13 @@
         <v>109</v>
       </c>
       <c r="BU8" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="BV8" t="s">
-        <v>121</v>
+        <v>111</v>
       </c>
       <c r="BW8" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
     </row>
     <row r="9" spans="1:75">
@@ -2643,64 +2604,64 @@
         <v>109</v>
       </c>
       <c r="S9" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="T9" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="U9" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="V9" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="W9" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="X9" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="Y9" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="Z9" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AA9" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AB9" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="AC9" t="s">
         <v>109</v>
       </c>
       <c r="AD9" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="AE9" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AF9" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AG9" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AH9" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AI9" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AJ9" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AK9" t="s">
         <v>109</v>
       </c>
       <c r="AL9" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AM9" t="s">
         <v>109</v>
@@ -2805,13 +2766,13 @@
         <v>109</v>
       </c>
       <c r="BU9" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="BV9" t="s">
-        <v>123</v>
+        <v>111</v>
       </c>
       <c r="BW9" t="s">
-        <v>120</v>
+        <v>111</v>
       </c>
     </row>
     <row r="10" spans="1:75">
@@ -2870,34 +2831,34 @@
         <v>109</v>
       </c>
       <c r="S10" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="T10" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="U10" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="V10" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="W10" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="X10" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="Y10" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="Z10" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AA10" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AB10" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AC10" t="s">
         <v>109</v>
@@ -2906,28 +2867,28 @@
         <v>109</v>
       </c>
       <c r="AE10" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AF10" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AG10" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AH10" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AI10" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AJ10" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AK10" t="s">
         <v>109</v>
       </c>
       <c r="AL10" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AM10" t="s">
         <v>109</v>
@@ -3032,13 +2993,13 @@
         <v>109</v>
       </c>
       <c r="BU10" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="BV10" t="s">
-        <v>122</v>
+        <v>111</v>
       </c>
       <c r="BW10" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
     </row>
     <row r="11" spans="1:75">
@@ -3097,22 +3058,22 @@
         <v>109</v>
       </c>
       <c r="S11" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="T11" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="U11" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="V11" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="W11" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="X11" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="Y11" t="s">
         <v>109</v>
@@ -3121,7 +3082,7 @@
         <v>109</v>
       </c>
       <c r="AA11" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="AB11" t="s">
         <v>109</v>
@@ -3133,22 +3094,22 @@
         <v>109</v>
       </c>
       <c r="AE11" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="AF11" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AG11" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AH11" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AI11" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AJ11" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AK11" t="s">
         <v>109</v>
@@ -3259,13 +3220,13 @@
         <v>109</v>
       </c>
       <c r="BU11" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="BV11" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="BW11" t="s">
-        <v>124</v>
+        <v>111</v>
       </c>
     </row>
     <row r="12" spans="1:75">
@@ -3324,64 +3285,64 @@
         <v>109</v>
       </c>
       <c r="S12" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="T12" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="U12" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="V12" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="W12" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="X12" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="Y12" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="Z12" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AA12" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AB12" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AC12" t="s">
         <v>109</v>
       </c>
       <c r="AD12" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AE12" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AF12" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AG12" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AH12" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AI12" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AJ12" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AK12" t="s">
         <v>109</v>
       </c>
       <c r="AL12" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AM12" t="s">
         <v>109</v>
@@ -3486,13 +3447,13 @@
         <v>109</v>
       </c>
       <c r="BU12" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="BV12" t="s">
-        <v>122</v>
+        <v>111</v>
       </c>
       <c r="BW12" t="s">
-        <v>120</v>
+        <v>111</v>
       </c>
     </row>
     <row r="13" spans="1:75">
@@ -3551,58 +3512,58 @@
         <v>109</v>
       </c>
       <c r="S13" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="T13" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="U13" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="V13" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="W13" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="X13" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="Y13" t="s">
         <v>109</v>
       </c>
       <c r="Z13" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AA13" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AB13" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="AC13" t="s">
         <v>109</v>
       </c>
       <c r="AD13" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="AE13" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AF13" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AG13" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AH13" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AI13" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AJ13" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AK13" t="s">
         <v>109</v>
@@ -3713,13 +3674,13 @@
         <v>109</v>
       </c>
       <c r="BU13" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="BV13" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="BW13" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
     </row>
     <row r="14" spans="1:75">
@@ -3778,31 +3739,31 @@
         <v>109</v>
       </c>
       <c r="S14" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="T14" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="U14" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="V14" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="W14" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="X14" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="Y14" t="s">
         <v>109</v>
       </c>
       <c r="Z14" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AA14" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AB14" t="s">
         <v>109</v>
@@ -3811,31 +3772,31 @@
         <v>109</v>
       </c>
       <c r="AD14" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AE14" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AF14" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AG14" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AH14" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AI14" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AJ14" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AK14" t="s">
         <v>109</v>
       </c>
       <c r="AL14" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AM14" t="s">
         <v>109</v>
@@ -3940,13 +3901,13 @@
         <v>109</v>
       </c>
       <c r="BU14" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="BV14" t="s">
-        <v>121</v>
+        <v>111</v>
       </c>
       <c r="BW14" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
     </row>
     <row r="15" spans="1:75">
@@ -4098,7 +4059,7 @@
         <v>110</v>
       </c>
       <c r="AX15" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AY15" t="s">
         <v>110</v>
@@ -4107,7 +4068,7 @@
         <v>109</v>
       </c>
       <c r="BA15" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="BB15" t="s">
         <v>109</v>
@@ -4125,10 +4086,10 @@
         <v>110</v>
       </c>
       <c r="BG15" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="BH15" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="BI15" t="s">
         <v>110</v>
@@ -4140,25 +4101,25 @@
         <v>110</v>
       </c>
       <c r="BL15" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="BM15" t="s">
         <v>110</v>
       </c>
       <c r="BN15" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="BO15" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="BP15" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="BQ15" t="s">
         <v>109</v>
       </c>
       <c r="BR15" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="BS15" t="s">
         <v>110</v>
@@ -4167,13 +4128,13 @@
         <v>110</v>
       </c>
       <c r="BU15" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="BV15" t="s">
-        <v>121</v>
+        <v>111</v>
       </c>
       <c r="BW15" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
     </row>
     <row r="16" spans="1:75">
@@ -4232,58 +4193,58 @@
         <v>109</v>
       </c>
       <c r="S16" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="T16" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="U16" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="V16" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="W16" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="X16" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="Y16" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="Z16" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AA16" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AB16" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AC16" t="s">
         <v>109</v>
       </c>
       <c r="AD16" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="AE16" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AF16" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AG16" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AH16" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AI16" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AJ16" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AK16" t="s">
         <v>109</v>
@@ -4394,13 +4355,13 @@
         <v>109</v>
       </c>
       <c r="BU16" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="BV16" t="s">
-        <v>122</v>
+        <v>111</v>
       </c>
       <c r="BW16" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
     </row>
     <row r="17" spans="1:75">
@@ -4459,64 +4420,64 @@
         <v>109</v>
       </c>
       <c r="S17" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="T17" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="U17" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="V17" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="W17" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="X17" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="Y17" t="s">
         <v>109</v>
       </c>
       <c r="Z17" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AA17" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AB17" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="AC17" t="s">
         <v>109</v>
       </c>
       <c r="AD17" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AE17" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AF17" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AG17" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AH17" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AI17" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AJ17" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AK17" t="s">
         <v>109</v>
       </c>
       <c r="AL17" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="AM17" t="s">
         <v>109</v>
@@ -4621,13 +4582,13 @@
         <v>109</v>
       </c>
       <c r="BU17" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="BV17" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="BW17" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
     </row>
     <row r="18" spans="1:75">
@@ -4686,34 +4647,34 @@
         <v>109</v>
       </c>
       <c r="S18" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="T18" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="U18" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="V18" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="W18" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="X18" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="Y18" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="Z18" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AA18" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AB18" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="AC18" t="s">
         <v>109</v>
@@ -4722,28 +4683,28 @@
         <v>109</v>
       </c>
       <c r="AE18" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AF18" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AG18" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AH18" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AI18" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AJ18" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AK18" t="s">
         <v>109</v>
       </c>
       <c r="AL18" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="AM18" t="s">
         <v>109</v>
@@ -4848,13 +4809,13 @@
         <v>109</v>
       </c>
       <c r="BU18" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="BV18" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="BW18" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
     </row>
     <row r="19" spans="1:75">
@@ -4913,31 +4874,31 @@
         <v>109</v>
       </c>
       <c r="S19" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="T19" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="U19" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="V19" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="W19" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="X19" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="Y19" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="Z19" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AA19" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AB19" t="s">
         <v>109</v>
@@ -4949,28 +4910,28 @@
         <v>109</v>
       </c>
       <c r="AE19" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AF19" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AG19" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AH19" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AI19" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AJ19" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AK19" t="s">
         <v>109</v>
       </c>
       <c r="AL19" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AM19" t="s">
         <v>109</v>
@@ -5075,13 +5036,13 @@
         <v>109</v>
       </c>
       <c r="BU19" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="BV19" t="s">
-        <v>121</v>
+        <v>111</v>
       </c>
       <c r="BW19" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
     </row>
     <row r="20" spans="1:75">
@@ -5140,31 +5101,31 @@
         <v>109</v>
       </c>
       <c r="S20" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="T20" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="U20" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="V20" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="W20" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="X20" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="Y20" t="s">
         <v>109</v>
       </c>
       <c r="Z20" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AA20" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AB20" t="s">
         <v>109</v>
@@ -5176,28 +5137,28 @@
         <v>109</v>
       </c>
       <c r="AE20" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AF20" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AG20" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AH20" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AI20" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AJ20" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AK20" t="s">
         <v>109</v>
       </c>
       <c r="AL20" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AM20" t="s">
         <v>109</v>
@@ -5302,13 +5263,13 @@
         <v>109</v>
       </c>
       <c r="BU20" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="BV20" t="s">
-        <v>121</v>
+        <v>111</v>
       </c>
       <c r="BW20" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="21" spans="1:75">
@@ -5367,34 +5328,34 @@
         <v>109</v>
       </c>
       <c r="S21" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="T21" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="U21" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="V21" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="W21" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="X21" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="Y21" t="s">
         <v>109</v>
       </c>
       <c r="Z21" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AA21" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AB21" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="AC21" t="s">
         <v>109</v>
@@ -5403,28 +5364,28 @@
         <v>109</v>
       </c>
       <c r="AE21" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AF21" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AG21" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AH21" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AI21" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AJ21" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AK21" t="s">
         <v>109</v>
       </c>
       <c r="AL21" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AM21" t="s">
         <v>109</v>
@@ -5529,13 +5490,13 @@
         <v>109</v>
       </c>
       <c r="BU21" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="BV21" t="s">
-        <v>122</v>
+        <v>111</v>
       </c>
       <c r="BW21" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
     </row>
     <row r="22" spans="1:75">
@@ -5594,34 +5555,34 @@
         <v>109</v>
       </c>
       <c r="S22" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="T22" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="U22" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="V22" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="W22" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="X22" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="Y22" t="s">
         <v>109</v>
       </c>
       <c r="Z22" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AA22" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AB22" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="AC22" t="s">
         <v>109</v>
@@ -5630,28 +5591,28 @@
         <v>109</v>
       </c>
       <c r="AE22" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AF22" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AG22" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AH22" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AI22" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AJ22" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AK22" t="s">
         <v>109</v>
       </c>
       <c r="AL22" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AM22" t="s">
         <v>109</v>
@@ -5756,13 +5717,13 @@
         <v>109</v>
       </c>
       <c r="BU22" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="BV22" t="s">
-        <v>122</v>
+        <v>111</v>
       </c>
       <c r="BW22" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
     </row>
     <row r="23" spans="1:75">
@@ -5821,31 +5782,31 @@
         <v>109</v>
       </c>
       <c r="S23" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="T23" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="U23" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="V23" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="W23" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="X23" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="Y23" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="Z23" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AA23" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AB23" t="s">
         <v>109</v>
@@ -5854,31 +5815,31 @@
         <v>109</v>
       </c>
       <c r="AD23" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="AE23" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AF23" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AG23" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AH23" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AI23" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AJ23" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AK23" t="s">
         <v>109</v>
       </c>
       <c r="AL23" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AM23" t="s">
         <v>109</v>
@@ -5983,13 +5944,13 @@
         <v>109</v>
       </c>
       <c r="BU23" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="BV23" t="s">
-        <v>122</v>
+        <v>111</v>
       </c>
       <c r="BW23" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
     </row>
     <row r="24" spans="1:75">
@@ -6048,34 +6009,34 @@
         <v>109</v>
       </c>
       <c r="S24" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="T24" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="U24" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="V24" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="W24" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="X24" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="Y24" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="Z24" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AA24" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AB24" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AC24" t="s">
         <v>109</v>
@@ -6084,28 +6045,28 @@
         <v>109</v>
       </c>
       <c r="AE24" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AF24" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AG24" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AH24" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AI24" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AJ24" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AK24" t="s">
         <v>109</v>
       </c>
       <c r="AL24" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AM24" t="s">
         <v>109</v>
@@ -6210,13 +6171,13 @@
         <v>109</v>
       </c>
       <c r="BU24" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="BV24" t="s">
-        <v>121</v>
+        <v>111</v>
       </c>
       <c r="BW24" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
     </row>
     <row r="25" spans="1:75">
@@ -6275,31 +6236,31 @@
         <v>109</v>
       </c>
       <c r="S25" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="T25" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="U25" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="V25" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="W25" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="X25" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="Y25" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="Z25" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AA25" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AB25" t="s">
         <v>109</v>
@@ -6311,28 +6272,28 @@
         <v>109</v>
       </c>
       <c r="AE25" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AF25" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AG25" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AH25" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AI25" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AJ25" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AK25" t="s">
         <v>109</v>
       </c>
       <c r="AL25" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="AM25" t="s">
         <v>109</v>
@@ -6437,13 +6398,13 @@
         <v>109</v>
       </c>
       <c r="BU25" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="BV25" t="s">
-        <v>122</v>
+        <v>111</v>
       </c>
       <c r="BW25" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
     </row>
     <row r="26" spans="1:75">
@@ -6502,31 +6463,31 @@
         <v>109</v>
       </c>
       <c r="S26" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="T26" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="U26" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="V26" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="W26" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="X26" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="Y26" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="Z26" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AA26" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AB26" t="s">
         <v>109</v>
@@ -6535,31 +6496,31 @@
         <v>109</v>
       </c>
       <c r="AD26" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="AE26" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AF26" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AG26" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AH26" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AI26" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AJ26" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AK26" t="s">
         <v>109</v>
       </c>
       <c r="AL26" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AM26" t="s">
         <v>109</v>
@@ -6664,13 +6625,13 @@
         <v>109</v>
       </c>
       <c r="BU26" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="BV26" t="s">
-        <v>122</v>
+        <v>111</v>
       </c>
       <c r="BW26" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
     </row>
     <row r="27" spans="1:75">
@@ -6735,10 +6696,10 @@
         <v>109</v>
       </c>
       <c r="U27" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="V27" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="W27" t="s">
         <v>109</v>
@@ -6891,13 +6852,13 @@
         <v>110</v>
       </c>
       <c r="BU27" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="BV27" t="s">
-        <v>121</v>
+        <v>111</v>
       </c>
       <c r="BW27" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
     </row>
     <row r="28" spans="1:75">
@@ -6956,64 +6917,64 @@
         <v>109</v>
       </c>
       <c r="S28" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="T28" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="U28" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="V28" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="W28" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="X28" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="Y28" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="Z28" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AA28" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AB28" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AC28" t="s">
         <v>109</v>
       </c>
       <c r="AD28" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AE28" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AF28" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AG28" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AH28" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AI28" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AJ28" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AK28" t="s">
         <v>109</v>
       </c>
       <c r="AL28" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AM28" t="s">
         <v>109</v>
@@ -7118,13 +7079,13 @@
         <v>109</v>
       </c>
       <c r="BU28" t="s">
-        <v>120</v>
+        <v>111</v>
       </c>
       <c r="BV28" t="s">
-        <v>121</v>
+        <v>111</v>
       </c>
       <c r="BW28" t="s">
-        <v>120</v>
+        <v>111</v>
       </c>
     </row>
     <row r="29" spans="1:75">
@@ -7183,31 +7144,31 @@
         <v>109</v>
       </c>
       <c r="S29" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="T29" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="U29" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="V29" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="W29" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="X29" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="Y29" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="Z29" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AA29" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AB29" t="s">
         <v>109</v>
@@ -7216,31 +7177,31 @@
         <v>109</v>
       </c>
       <c r="AD29" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="AE29" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AF29" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AG29" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AH29" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AI29" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AJ29" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AK29" t="s">
         <v>109</v>
       </c>
       <c r="AL29" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AM29" t="s">
         <v>109</v>
@@ -7345,13 +7306,13 @@
         <v>109</v>
       </c>
       <c r="BU29" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="BV29" t="s">
-        <v>122</v>
+        <v>111</v>
       </c>
       <c r="BW29" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
     </row>
     <row r="30" spans="1:75">
@@ -7407,34 +7368,34 @@
         <v>109</v>
       </c>
       <c r="R30" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="S30" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="T30" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="U30" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="V30" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="W30" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="X30" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="Y30" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="Z30" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AA30" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AB30" t="s">
         <v>109</v>
@@ -7443,31 +7404,31 @@
         <v>109</v>
       </c>
       <c r="AD30" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AE30" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AF30" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AG30" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AH30" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AI30" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AJ30" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AK30" t="s">
         <v>109</v>
       </c>
       <c r="AL30" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="AM30" t="s">
         <v>109</v>
@@ -7572,13 +7533,13 @@
         <v>109</v>
       </c>
       <c r="BU30" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="BV30" t="s">
-        <v>122</v>
+        <v>111</v>
       </c>
       <c r="BW30" t="s">
-        <v>120</v>
+        <v>111</v>
       </c>
     </row>
     <row r="31" spans="1:75">
@@ -7637,31 +7598,31 @@
         <v>109</v>
       </c>
       <c r="S31" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="T31" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="U31" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="V31" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="W31" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="X31" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="Y31" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="Z31" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AA31" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AB31" t="s">
         <v>109</v>
@@ -7670,31 +7631,31 @@
         <v>109</v>
       </c>
       <c r="AD31" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AE31" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AF31" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AG31" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AH31" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AI31" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AJ31" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AK31" t="s">
         <v>109</v>
       </c>
       <c r="AL31" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AM31" t="s">
         <v>109</v>
@@ -7799,13 +7760,13 @@
         <v>109</v>
       </c>
       <c r="BU31" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="BV31" t="s">
-        <v>121</v>
+        <v>111</v>
       </c>
       <c r="BW31" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
     </row>
     <row r="32" spans="1:75">
@@ -7864,64 +7825,64 @@
         <v>109</v>
       </c>
       <c r="S32" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="T32" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="U32" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="V32" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="W32" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="X32" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="Y32" t="s">
         <v>109</v>
       </c>
       <c r="Z32" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AA32" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AB32" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AC32" t="s">
         <v>109</v>
       </c>
       <c r="AD32" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AE32" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AF32" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AG32" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AH32" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AI32" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AJ32" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AK32" t="s">
         <v>109</v>
       </c>
       <c r="AL32" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AM32" t="s">
         <v>109</v>
@@ -8026,13 +7987,13 @@
         <v>109</v>
       </c>
       <c r="BU32" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="BV32" t="s">
-        <v>121</v>
+        <v>111</v>
       </c>
       <c r="BW32" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
     </row>
     <row r="33" spans="1:75">
@@ -8091,64 +8052,64 @@
         <v>109</v>
       </c>
       <c r="S33" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="T33" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="U33" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="V33" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="W33" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="X33" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="Y33" t="s">
         <v>109</v>
       </c>
       <c r="Z33" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AA33" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AB33" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AC33" t="s">
         <v>109</v>
       </c>
       <c r="AD33" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AE33" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AF33" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AG33" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AH33" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AI33" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AJ33" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AK33" t="s">
         <v>109</v>
       </c>
       <c r="AL33" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AM33" t="s">
         <v>109</v>
@@ -8253,13 +8214,13 @@
         <v>109</v>
       </c>
       <c r="BU33" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="BV33" t="s">
-        <v>121</v>
+        <v>111</v>
       </c>
       <c r="BW33" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
     </row>
     <row r="34" spans="1:75">
@@ -8318,31 +8279,31 @@
         <v>109</v>
       </c>
       <c r="S34" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="T34" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="U34" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="V34" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="W34" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="X34" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="Y34" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="Z34" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AA34" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AB34" t="s">
         <v>109</v>
@@ -8351,31 +8312,31 @@
         <v>109</v>
       </c>
       <c r="AD34" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="AE34" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="AF34" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AG34" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AH34" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AI34" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AJ34" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AK34" t="s">
         <v>109</v>
       </c>
       <c r="AL34" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AM34" t="s">
         <v>109</v>
@@ -8480,13 +8441,13 @@
         <v>109</v>
       </c>
       <c r="BU34" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="BV34" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="BW34" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
     </row>
     <row r="35" spans="1:75">
@@ -8545,31 +8506,31 @@
         <v>109</v>
       </c>
       <c r="S35" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="T35" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="U35" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="V35" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="W35" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="X35" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="Y35" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="Z35" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AA35" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AB35" t="s">
         <v>109</v>
@@ -8581,22 +8542,22 @@
         <v>109</v>
       </c>
       <c r="AE35" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AF35" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AG35" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AH35" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AI35" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AJ35" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AK35" t="s">
         <v>109</v>
@@ -8707,13 +8668,13 @@
         <v>109</v>
       </c>
       <c r="BU35" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="BV35" t="s">
-        <v>121</v>
+        <v>111</v>
       </c>
       <c r="BW35" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/Exchange_rate_percentile_classification_matrix.xlsx
+++ b/outputs/Exchange_rate_percentile_classification_matrix.xlsx
@@ -343,7 +343,7 @@
     <t>Zabul</t>
   </si>
   <si>
-    <t>Minimal</t>
+    <t>No concern</t>
   </si>
   <si>
     <t>No data</t>
